--- a/data/trans_orig/P1417-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2007</t>
+          <t>Población con diagnóstico de anemia en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8063</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5409</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9384</t>
+          <t>9581</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,79%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264947</t>
+          <t>264998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255429</t>
+          <t>254457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524464</t>
+          <t>524267</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>10494</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5886</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>18360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6460</t>
+          <t>6821</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21626</t>
+          <t>22286</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>484407</t>
+          <t>482581</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484911</t>
+          <t>485589</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498063</t>
+          <t>498159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>975398</t>
+          <t>974738</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990564</t>
+          <t>990203</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,32%</t>
         </is>
       </c>
     </row>
@@ -1419,82 +1419,82 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2911</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,87%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,62%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,3%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>2911</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7885</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2911</t>
-        </is>
-      </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>915</t>
+          <t>910</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>7906</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,21%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>316878</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>318846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327527</t>
+          <t>327712</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646295</t>
+          <t>646352</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653343</t>
+          <t>653348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>4736</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1721</t>
+          <t>1809</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9712</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2646</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12023</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353518</t>
+          <t>353935</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361744</t>
+          <t>361597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369735</t>
+          <t>369647</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718104</t>
+          <t>718974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>727481</t>
+          <t>728243</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4625</t>
+          <t>3758</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2984</t>
+          <t>2160</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12963</t>
+          <t>12930</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3070</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14402</t>
+          <t>14784</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,6%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>198683</t>
+          <t>199550</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194705</t>
+          <t>194738</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204684</t>
+          <t>205508</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396574</t>
+          <t>396192</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407906</t>
+          <t>407932</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>268864</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>270811</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269920</t>
+          <t>269943</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277135</t>
+          <t>277131</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>539741</t>
+          <t>540721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547938</t>
+          <t>547947</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8792</t>
+          <t>9277</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>26186</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11821</t>
+          <t>11505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>30611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>606235</t>
+          <t>605750</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614036</t>
+          <t>614096</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,84%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>612823</t>
+          <t>612033</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>629795</t>
+          <t>628795</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1223537</t>
+          <t>1222635</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1241425</t>
+          <t>1241741</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10051</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7222</t>
+          <t>7375</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21020</t>
+          <t>20892</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28221</t>
+          <t>28251</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>733744</t>
+          <t>733223</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>762491</t>
+          <t>762619</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776289</t>
+          <t>776136</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1499085</t>
+          <t>1499055</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1516359</t>
+          <t>1516541</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7344</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22702</t>
+          <t>22078</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43270</t>
+          <t>43609</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>73613</t>
+          <t>74177</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56139</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89961</t>
+          <t>89947</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3253841</t>
+          <t>3254465</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3269786</t>
+          <t>3269199</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3305584</t>
+          <t>3305020</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3335927</t>
+          <t>3335588</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6565780</t>
+          <t>6565794</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6599602</t>
+          <t>6601654</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2012</t>
+          <t>Población con diagnóstico de anemia en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>5994</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>5053</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18350</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19231</t>
+          <t>18894</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>287796</t>
+          <t>288744</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>269211</t>
+          <t>268895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282312</t>
+          <t>282192</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>562752</t>
+          <t>563089</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>575712</t>
+          <t>576491</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2052</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4968</t>
+          <t>4977</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18827</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5149</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18469</t>
+          <t>18752</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>503475</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505527</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>504938</t>
+          <t>505830</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518797</t>
+          <t>518788</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010823</t>
+          <t>1010540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024143</t>
+          <t>1024070</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6716</t>
+          <t>6871</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3038</t>
+          <t>2168</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>12494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4052</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15497</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317330</t>
+          <t>317175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328289</t>
+          <t>328526</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337982</t>
+          <t>338852</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649569</t>
+          <t>649153</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661014</t>
+          <t>660992</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2081</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8930</t>
+          <t>9852</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25598</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8919</t>
+          <t>9145</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>24845</t>
+          <t>25642</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>371901</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>373982</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>363353</t>
+          <t>362923</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>380021</t>
+          <t>379099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>738088</t>
+          <t>737291</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>754014</t>
+          <t>753788</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>977</t>
+          <t>986</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8390</t>
+          <t>9912</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>20929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8366</t>
+          <t>8935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>24870</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>204228</t>
+          <t>202706</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211641</t>
+          <t>211632</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198719</t>
+          <t>198662</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213669</t>
+          <t>213574</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407144</t>
+          <t>407339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423843</t>
+          <t>423274</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>97,93%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7022</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10295</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2974</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>266959</t>
+          <t>267195</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267801</t>
+          <t>267349</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>538169</t>
+          <t>537448</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549103</t>
+          <t>549130</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6521</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12222</t>
+          <t>12188</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32092</t>
+          <t>32607</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>14251</t>
+          <t>13450</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>34612</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656664</t>
+          <t>656267</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>661761</t>
+          <t>661246</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681631</t>
+          <t>681665</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1321702</t>
+          <t>1322029</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1342390</t>
+          <t>1343191</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,01%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9622</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,42 +6477,42 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>17128</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>10189</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>27077</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,08%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>17128</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>10437</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>27872</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>13569</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32494</t>
+          <t>32553</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>769476</t>
+          <t>768275</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>777985</t>
+          <t>778001</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,49 +6585,49 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>739</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>804403</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>794454</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>811342</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>97,92%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>96,7%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>98,76%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>99,86%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>804403</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>793659</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>811094</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>97,92%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>1452</t>
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1568135</t>
+          <t>1568076</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1587594</t>
+          <t>1587060</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>8263</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>24647</t>
+          <t>23462</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>78350</t>
+          <t>77799</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>119082</t>
+          <t>118642</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>92184</t>
+          <t>89615</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>136637</t>
+          <t>132235</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3402132</t>
+          <t>3403317</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3418516</t>
+          <t>3417749</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3434970</t>
+          <t>3435410</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3475702</t>
+          <t>3476253</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6844194</t>
+          <t>6848596</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6888647</t>
+          <t>6891216</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,72%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2016</t>
+          <t>Población con diagnóstico de anemia en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9690</t>
+          <t>9458</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15882</t>
+          <t>17024</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5155</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20117</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284071</t>
+          <t>284303</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>272821</t>
+          <t>271679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285478</t>
+          <t>285377</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>562347</t>
+          <t>561139</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577309</t>
+          <t>577241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10397</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1095</t>
+          <t>1085</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>10900</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16183</t>
+          <t>15703</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492178</t>
+          <t>492325</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512107</t>
+          <t>512184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521989</t>
+          <t>521999</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009476</t>
+          <t>1009956</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021578</t>
+          <t>1021597</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3674</t>
+          <t>3960</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>2817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13331</t>
+          <t>13212</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3036</t>
+          <t>3639</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13914</t>
+          <t>15399</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314891</t>
+          <t>314605</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322978</t>
+          <t>323097</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333337</t>
+          <t>333492</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>640960</t>
+          <t>639475</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651838</t>
+          <t>651235</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9791</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8339</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24705</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11684</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29378</t>
+          <t>28600</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360201</t>
+          <t>360173</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368933</t>
+          <t>368929</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362578</t>
+          <t>362183</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>379150</t>
+          <t>378944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>727869</t>
+          <t>728647</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>745563</t>
+          <t>745160</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>5361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>2222</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12121</t>
+          <t>12402</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2943</t>
+          <t>3019</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14055</t>
+          <t>13832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>206278</t>
+          <t>205860</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206466</t>
+          <t>206185</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216518</t>
+          <t>216365</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415753</t>
+          <t>415976</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426865</t>
+          <t>426789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>802</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8925</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1200</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11334</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14458</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254198</t>
+          <t>254926</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262335</t>
+          <t>262321</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>261781</t>
+          <t>262854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271852</t>
+          <t>271915</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521780</t>
+          <t>521901</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>532997</t>
+          <t>533345</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7212</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13812</t>
+          <t>13495</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32079</t>
+          <t>32244</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15185</t>
+          <t>15425</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34643</t>
+          <t>35402</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649346</t>
+          <t>649325</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>655673</t>
+          <t>656558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,87%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>659215</t>
+          <t>659050</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>677482</t>
+          <t>677799</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1313209</t>
+          <t>1312450</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1332667</t>
+          <t>1332427</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5662</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13657</t>
+          <t>13476</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>31767</t>
+          <t>32055</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14038</t>
+          <t>13612</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>34762</t>
+          <t>32811</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,04%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>772949</t>
+          <t>772921</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>794400</t>
+          <t>794112</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>812510</t>
+          <t>812691</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1569988</t>
+          <t>1571939</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1590712</t>
+          <t>1591138</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30285</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>70053</t>
+          <t>70214</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>110177</t>
+          <t>107871</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>85304</t>
+          <t>87871</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>126421</t>
+          <t>130168</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3364065</t>
+          <t>3364774</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3382294</t>
+          <t>3382214</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3434365</t>
+          <t>3436671</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3474489</t>
+          <t>3474328</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6812471</t>
+          <t>6808724</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6853588</t>
+          <t>6851021</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de anemia en 2023</t>
+          <t>Población con diagnóstico de anemia en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>786</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7855</t>
+          <t>7663</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9251</t>
+          <t>8940</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>34035</t>
+          <t>32344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,47 +10752,47 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>11,17%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>19194</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>11313</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>40908</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
           <t>3,19%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>11,75%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>19194</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>11036</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>39876</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303588</t>
+          <t>303780</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310549</t>
+          <t>310657</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>255600</t>
+          <t>257291</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280384</t>
+          <t>280695</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,47 +10865,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>581883</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>560169</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>589764</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
           <t>96,81%</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>581883</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>561201</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>590041</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28906</t>
+          <t>29110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11100,7 +11100,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17225</t>
+          <t>16423</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33828</t>
+          <t>33944</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505939</t>
+          <t>505907</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514758</t>
+          <t>515161</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>484149</t>
+          <t>483945</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499270</t>
+          <t>499240</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>995307</t>
+          <t>995191</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1011910</t>
+          <t>1012712</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7315</t>
+          <t>8016</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7438</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17767</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9977</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22203</t>
+          <t>21898</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308735</t>
+          <t>308034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314837</t>
+          <t>314770</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331361</t>
+          <t>331407</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341690</t>
+          <t>341807</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>642975</t>
+          <t>643280</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655201</t>
+          <t>655424</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8224</t>
+          <t>7605</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9616</t>
+          <t>9975</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26749</t>
+          <t>27288</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30293</t>
+          <t>31078</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304333</t>
+          <t>304952</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>311125</t>
+          <t>310877</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448969</t>
+          <t>448430</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>466102</t>
+          <t>465743</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>757981</t>
+          <t>757196</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>774659</t>
+          <t>774816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3603</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>4231</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11092</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>11914</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -12187,7 +12187,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175653</t>
+          <t>175139</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -12202,7 +12202,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>196881</t>
+          <t>197097</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>204044</t>
+          <t>203742</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>374800</t>
+          <t>373902</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>381852</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15175</t>
+          <t>15334</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9831</t>
+          <t>9929</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20457</t>
+          <t>20898</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18366</t>
+          <t>18091</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>32748</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,23%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254461</t>
+          <t>254302</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263967</t>
+          <t>263516</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235930</t>
+          <t>235489</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246556</t>
+          <t>246458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,02%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493423</t>
+          <t>493275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507657</t>
+          <t>507932</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,56%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5929</t>
+          <t>6021</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17675</t>
+          <t>18747</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>22961</t>
+          <t>26212</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78716</t>
+          <t>78940</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>39341</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85837</t>
+          <t>85352</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>603906</t>
+          <t>602834</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>615652</t>
+          <t>615560</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>768743</t>
+          <t>768519</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>824498</t>
+          <t>821247</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1383203</t>
+          <t>1383688</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1426664</t>
+          <t>1429699</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,16%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,32%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>359</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7000</t>
+          <t>7512</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5824</t>
+          <t>5718</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16324</t>
+          <t>16808</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6926</t>
+          <t>6510</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20993</t>
+          <t>20618</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>921720</t>
+          <t>921208</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>928361</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>698517</t>
+          <t>698033</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>709017</t>
+          <t>709123</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1622568</t>
+          <t>1622943</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1636635</t>
+          <t>1637051</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>26685</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>51180</t>
+          <t>50183</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>124424</t>
+          <t>124627</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>179045</t>
+          <t>180486</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>161067</t>
+          <t>165015</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>221119</t>
+          <t>219937</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3403629</t>
+          <t>3404626</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3426763</t>
+          <t>3428124</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3475149</t>
+          <t>3473708</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3529770</t>
+          <t>3529567</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6887884</t>
+          <t>6889066</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6947936</t>
+          <t>6943988</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1417-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1417-Provincia-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>5470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9581</t>
+          <t>9084</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>264998</t>
+          <t>265041</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>254457</t>
+          <t>255368</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>524267</t>
+          <t>524764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10494</t>
+          <t>7513</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5790</t>
+          <t>5749</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18360</t>
+          <t>18780</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6821</t>
+          <t>6999</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22286</t>
+          <t>21917</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>482581</t>
+          <t>485562</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485589</t>
+          <t>485169</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>498159</t>
+          <t>498200</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>974738</t>
+          <t>975107</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>990203</t>
+          <t>990025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7700</t>
+          <t>7821</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>911</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7906</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>327712</t>
+          <t>327591</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>335412</t>
+          <t>334507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>646352</t>
+          <t>646498</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>653348</t>
+          <t>653347</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4736</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1809</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9859</t>
+          <t>10475</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1884</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11153</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>353935</t>
+          <t>353337</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>361597</t>
+          <t>360981</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>369647</t>
+          <t>369719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>718974</t>
+          <t>718251</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>728243</t>
+          <t>728230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2160</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>12915</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14784</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>199550</t>
+          <t>200012</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194738</t>
+          <t>194753</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>205508</t>
+          <t>205422</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>396192</t>
+          <t>396701</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>407932</t>
+          <t>407952</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8278</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8234</t>
+          <t>8193</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>269943</t>
+          <t>269866</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>277131</t>
+          <t>277130</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>540721</t>
+          <t>540762</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>547947</t>
+          <t>547952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>943</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9277</t>
+          <t>8382</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9424</t>
+          <t>8474</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26186</t>
+          <t>25212</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>11505</t>
+          <t>11344</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>30611</t>
+          <t>29537</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>605750</t>
+          <t>606645</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>614096</t>
+          <t>614084</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>612033</t>
+          <t>613007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>628795</t>
+          <t>629745</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1222635</t>
+          <t>1223709</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1241741</t>
+          <t>1241902</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10572</t>
+          <t>10571</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7375</t>
+          <t>7180</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20892</t>
+          <t>21533</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10651</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>27897</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>733223</t>
+          <t>733224</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>741987</t>
+          <t>741976</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>762619</t>
+          <t>761978</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>776136</t>
+          <t>776331</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1499055</t>
+          <t>1499409</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1516541</t>
+          <t>1516655</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>7344</t>
+          <t>7324</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>22078</t>
+          <t>22343</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>43609</t>
+          <t>43731</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>74177</t>
+          <t>75000</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>54087</t>
+          <t>54059</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>89947</t>
+          <t>89366</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3254465</t>
+          <t>3254200</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3269199</t>
+          <t>3269219</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3305020</t>
+          <t>3304197</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3335588</t>
+          <t>3335466</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6565794</t>
+          <t>6566375</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6601654</t>
+          <t>6601682</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>6822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4076,7 +4076,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18350</t>
+          <t>16961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>6040</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>19910</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288744</t>
+          <t>287916</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4184,7 +4184,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>268895</t>
+          <t>270284</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>282192</t>
+          <t>282925</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>563089</t>
+          <t>562073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>576491</t>
+          <t>575943</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4977</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17935</t>
+          <t>17890</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>5222</t>
+          <t>5133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18752</t>
+          <t>18862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>505830</t>
+          <t>505875</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>518788</t>
+          <t>518585</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4567,7 +4567,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1010540</t>
+          <t>1010430</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1024070</t>
+          <t>1024159</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6354</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4762,7 +4762,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2148</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>12496</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4074</t>
+          <t>4041</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15913</t>
+          <t>15497</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>317175</t>
+          <t>317692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>328526</t>
+          <t>328524</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>338852</t>
+          <t>338872</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4910,7 +4910,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>649153</t>
+          <t>649569</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>660992</t>
+          <t>661025</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,7 +4940,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9335</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26028</t>
+          <t>26548</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9145</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25642</t>
+          <t>25801</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362923</t>
+          <t>362403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>379099</t>
+          <t>379616</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>737291</t>
+          <t>737132</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>753788</t>
+          <t>754087</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>986</t>
+          <t>975</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>8587</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20929</t>
+          <t>21020</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8935</t>
+          <t>8111</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24870</t>
+          <t>25169</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>202706</t>
+          <t>204031</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>211632</t>
+          <t>211643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>198662</t>
+          <t>198571</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>213574</t>
+          <t>213620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>407339</t>
+          <t>407040</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>423274</t>
+          <t>424098</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6786</t>
+          <t>7028</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1929</t>
+          <t>1941</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10747</t>
+          <t>10769</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2964</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>267195</t>
+          <t>266953</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>267349</t>
+          <t>267327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>276167</t>
+          <t>276155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>537448</t>
+          <t>538182</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>549130</t>
+          <t>549113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>12188</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32607</t>
+          <t>33883</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>14430</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34612</t>
+          <t>35733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>656267</t>
+          <t>655766</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -6242,7 +6242,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>661246</t>
+          <t>659970</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>681665</t>
+          <t>680848</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1322029</t>
+          <t>1320908</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1343191</t>
+          <t>1342211</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,94%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>10616</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10189</t>
+          <t>9673</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27077</t>
+          <t>26309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13569</t>
+          <t>13055</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32553</t>
+          <t>31433</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>768275</t>
+          <t>768482</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>778001</t>
+          <t>778038</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>794454</t>
+          <t>795222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>811342</t>
+          <t>811858</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1568076</t>
+          <t>1569196</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1587060</t>
+          <t>1587574</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>9030</t>
+          <t>8302</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>23462</t>
+          <t>24472</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>77799</t>
+          <t>78955</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>118642</t>
+          <t>117794</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>89615</t>
+          <t>94271</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>132235</t>
+          <t>137955</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3403317</t>
+          <t>3402307</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3417749</t>
+          <t>3418477</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3435410</t>
+          <t>3436258</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3476253</t>
+          <t>3475097</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6848596</t>
+          <t>6842876</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6891216</t>
+          <t>6886560</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,65%</t>
         </is>
       </c>
     </row>
@@ -7384,7 +7384,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9458</t>
+          <t>9882</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7399,7 +7399,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3252</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>17024</t>
+          <t>15905</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>4857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>20118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -7492,7 +7492,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>284303</t>
+          <t>283879</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>271679</t>
+          <t>272798</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>285377</t>
+          <t>285451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>561139</t>
+          <t>562346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>577241</t>
+          <t>577607</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1032</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10250</t>
+          <t>9385</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>1094</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10900</t>
+          <t>10916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7777,7 +7777,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4089</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>15830</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>492325</t>
+          <t>493190</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>501543</t>
+          <t>501533</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,7 +7850,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>512184</t>
+          <t>512168</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>521999</t>
+          <t>521990</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,7 +7885,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1009956</t>
+          <t>1009829</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1021597</t>
+          <t>1021570</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3960</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2817</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>13212</t>
+          <t>13828</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3639</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15399</t>
+          <t>14439</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,2%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>314605</t>
+          <t>313484</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>323097</t>
+          <t>322481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>333492</t>
+          <t>333317</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>639475</t>
+          <t>640435</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>651235</t>
+          <t>651469</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>974</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9791</t>
+          <t>8934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8339</t>
+          <t>7873</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25100</t>
+          <t>24078</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28600</t>
+          <t>28929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>360173</t>
+          <t>361030</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>368929</t>
+          <t>368990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>362183</t>
+          <t>363205</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>378944</t>
+          <t>379410</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>728647</t>
+          <t>728318</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>745160</t>
+          <t>746013</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5361</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8771,7 +8771,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2139</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>13562</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3024</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13832</t>
+          <t>13422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8841,7 +8841,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>205860</t>
+          <t>206337</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -8879,7 +8879,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>206185</t>
+          <t>205025</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216365</t>
+          <t>216448</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>415976</t>
+          <t>416386</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>426789</t>
+          <t>426784</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,7 +8949,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>802</t>
+          <t>790</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8197</t>
+          <t>8504</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1200</t>
+          <t>1184</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>10261</t>
+          <t>10044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14337</t>
+          <t>14957</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254926</t>
+          <t>254619</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>262321</t>
+          <t>262333</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>262854</t>
+          <t>263071</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>271915</t>
+          <t>271931</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>521901</t>
+          <t>521281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>533345</t>
+          <t>533009</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,4%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>7176</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13495</t>
+          <t>13518</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32244</t>
+          <t>31624</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15425</t>
+          <t>15215</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35402</t>
+          <t>35588</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>649325</t>
+          <t>649382</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>656558</t>
+          <t>655672</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>659050</t>
+          <t>659670</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>677799</t>
+          <t>677776</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1312450</t>
+          <t>1312264</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1332427</t>
+          <t>1332637</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -9785,7 +9785,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5662</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13476</t>
+          <t>13381</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>32055</t>
+          <t>32143</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13612</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32811</t>
+          <t>33214</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>772921</t>
+          <t>773407</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>794112</t>
+          <t>794024</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>812691</t>
+          <t>812786</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1571939</t>
+          <t>1571536</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1591138</t>
+          <t>1591402</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12062</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>30491</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10143,7 +10143,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>70214</t>
+          <t>68985</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>107871</t>
+          <t>106283</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>87871</t>
+          <t>87288</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>130168</t>
+          <t>128433</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3364774</t>
+          <t>3363859</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3382214</t>
+          <t>3382288</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3436671</t>
+          <t>3438259</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3474328</t>
+          <t>3475557</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6808724</t>
+          <t>6810459</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6851021</t>
+          <t>6851604</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,74%</t>
         </is>
       </c>
     </row>
@@ -10697,22 +10697,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3142</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>786</t>
+          <t>799</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7663</t>
+          <t>7795</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>16052</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8940</t>
+          <t>8247</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32344</t>
+          <t>23291</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>19194</t>
+          <t>16653</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11313</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>26837</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -10810,27 +10810,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>308301</t>
+          <t>315748</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>303780</t>
+          <t>311050</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>310657</t>
+          <t>318046</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>273583</t>
+          <t>302505</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>257291</t>
+          <t>292770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>280695</t>
+          <t>307814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>581883</t>
+          <t>618253</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>560169</t>
+          <t>608069</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>589764</t>
+          <t>624456</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3945</t>
+          <t>4045</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>924</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>10600</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20519</t>
+          <t>20487</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13815</t>
+          <t>14353</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29110</t>
+          <t>29030</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>24465</t>
+          <t>24531</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16423</t>
+          <t>17107</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33944</t>
+          <t>33941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>512135</t>
+          <t>524281</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505907</t>
+          <t>517726</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>515161</t>
+          <t>527402</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>492536</t>
+          <t>524054</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>483945</t>
+          <t>515511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>499240</t>
+          <t>530188</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1004670</t>
+          <t>1048336</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>995191</t>
+          <t>1038926</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1012712</t>
+          <t>1055760</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516080</t>
+          <t>528326</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516080</t>
+          <t>528326</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516080</t>
+          <t>528326</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>513055</t>
+          <t>544541</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>513055</t>
+          <t>544541</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>513055</t>
+          <t>544541</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1029135</t>
+          <t>1072867</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1029135</t>
+          <t>1072867</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1029135</t>
+          <t>1072867</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3628</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8016</t>
+          <t>7263</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11663</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7741</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>18405</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>15290</t>
+          <t>15660</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9754</t>
+          <t>10683</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21898</t>
+          <t>22517</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>312422</t>
+          <t>312381</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>308034</t>
+          <t>308730</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>314770</t>
+          <t>314703</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>337465</t>
+          <t>344333</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>331407</t>
+          <t>337976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341807</t>
+          <t>348640</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>649888</t>
+          <t>656715</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>643280</t>
+          <t>649858</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>655424</t>
+          <t>661692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>349128</t>
+          <t>356381</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>665178</t>
+          <t>672375</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3915</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1680</t>
+          <t>1878</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7605</t>
+          <t>9588</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17017</t>
+          <t>18638</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>11992</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27288</t>
+          <t>27715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20933</t>
+          <t>23391</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13458</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31078</t>
+          <t>33937</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>308642</t>
+          <t>368393</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>304952</t>
+          <t>363557</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>310877</t>
+          <t>371267</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>458701</t>
+          <t>403323</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>448430</t>
+          <t>394246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>465743</t>
+          <t>409969</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>767341</t>
+          <t>771716</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>757196</t>
+          <t>761170</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>774816</t>
+          <t>778824</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1005</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12079,12 +12079,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3603</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>6961</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4231</t>
+          <t>4340</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>11780</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>7966</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5104</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -12182,27 +12182,27 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>177737</t>
+          <t>204624</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>175139</t>
+          <t>202492</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>201012</t>
+          <t>219110</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>197097</t>
+          <t>214761</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203742</t>
+          <t>222201</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>378748</t>
+          <t>423733</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>373902</t>
+          <t>418839</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>381610</t>
+          <t>426872</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>207973</t>
+          <t>226541</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207973</t>
+          <t>226541</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>207973</t>
+          <t>226541</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386714</t>
+          <t>432206</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386714</t>
+          <t>432206</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386714</t>
+          <t>432206</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>9702</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>15334</t>
+          <t>15149</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>14501</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>10024</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>20898</t>
+          <t>20829</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>24300</t>
+          <t>24125</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>18091</t>
+          <t>18265</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>32748</t>
+          <t>32669</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>259837</t>
+          <t>261005</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>254302</t>
+          <t>255558</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>263516</t>
+          <t>264827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>241886</t>
+          <t>248676</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235489</t>
+          <t>242270</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246458</t>
+          <t>253075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>501723</t>
+          <t>509681</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>493275</t>
+          <t>501137</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507932</t>
+          <t>515541</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>256387</t>
+          <t>263099</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526023</t>
+          <t>533806</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>14677</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6021</t>
+          <t>8553</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18747</t>
+          <t>24638</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>56083</t>
+          <t>70091</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26212</t>
+          <t>56824</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>78940</t>
+          <t>87394</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>66892</t>
+          <t>84768</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39341</t>
+          <t>67516</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>85352</t>
+          <t>101985</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,86%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>610772</t>
+          <t>701766</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>602834</t>
+          <t>691805</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>615560</t>
+          <t>707890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>791376</t>
+          <t>699923</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>768519</t>
+          <t>682620</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>821247</t>
+          <t>713190</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1402148</t>
+          <t>1401689</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1383688</t>
+          <t>1384472</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1429699</t>
+          <t>1418941</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>95,46%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>621581</t>
+          <t>716443</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>621581</t>
+          <t>716443</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>621581</t>
+          <t>716443</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>847459</t>
+          <t>770014</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>847459</t>
+          <t>770014</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>847459</t>
+          <t>770014</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1469040</t>
+          <t>1486457</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1469040</t>
+          <t>1486457</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1469040</t>
+          <t>1486457</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2519</t>
+          <t>2827</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7512</t>
+          <t>8136</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>11809</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5718</t>
+          <t>6894</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16808</t>
+          <t>20541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6510</t>
+          <t>8422</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20618</t>
+          <t>23859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>926201</t>
+          <t>795245</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>921208</t>
+          <t>789936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>928361</t>
+          <t>797332</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,96%</t>
+          <t>99,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>704563</t>
+          <t>818184</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>698033</t>
+          <t>809452</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>709123</t>
+          <t>823099</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1630764</t>
+          <t>1613429</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1622943</t>
+          <t>1604206</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1637051</t>
+          <t>1619643</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,48%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>714841</t>
+          <t>829993</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>714841</t>
+          <t>829993</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>714841</t>
+          <t>829993</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1643561</t>
+          <t>1628065</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1643561</t>
+          <t>1628065</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1643561</t>
+          <t>1628065</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26685</t>
+          <t>34099</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50183</t>
+          <t>57097</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>153074</t>
+          <t>168484</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>124627</t>
+          <t>146499</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>180486</t>
+          <t>189643</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>191837</t>
+          <t>212236</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>165015</t>
+          <t>189004</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>219937</t>
+          <t>238462</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3416046</t>
+          <t>3483444</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3404626</t>
+          <t>3470100</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3428124</t>
+          <t>3493098</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3501120</t>
+          <t>3560108</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3473708</t>
+          <t>3538949</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3529567</t>
+          <t>3582093</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6917166</t>
+          <t>7043553</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6889066</t>
+          <t>7017327</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6943988</t>
+          <t>7066785</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,4%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3454809</t>
+          <t>3527197</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3654194</t>
+          <t>3728592</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7109003</t>
+          <t>7255789</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
